--- a/salaryEmail/示例数据/通讯录.xlsx
+++ b/salaryEmail/示例数据/通讯录.xlsx
@@ -43,7 +43,7 @@
     <t>技术部</t>
   </si>
   <si>
-    <t/>
+    <t>0000</t>
   </si>
 </sst>
 </file>
